--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3112,6 +3112,990 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128353772</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79063</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>185</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>471220</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6871890</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128353867</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80134</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>471215</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6871869</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128353668</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79063</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>185</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>471209</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6871890</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128352854</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>471288</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6871854</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128354191</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>471282</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6871838</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128352646</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78698</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>353</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>471311</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6871830</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128353533</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79110</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>864</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>471206</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6871904</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128354107</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>471246</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6871875</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128353959</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>471204</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6871867</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128353844</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>olremmet, olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>471221</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6871873</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>128353772</v>
       </c>
       <c r="B25" t="n">
-        <v>79063</v>
+        <v>79064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128353867</v>
       </c>
       <c r="B26" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128353668</v>
       </c>
       <c r="B27" t="n">
-        <v>79063</v>
+        <v>79064</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>128352854</v>
       </c>
       <c r="B28" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128354191</v>
       </c>
       <c r="B29" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>128352646</v>
       </c>
       <c r="B30" t="n">
-        <v>78698</v>
+        <v>78699</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128353533</v>
       </c>
       <c r="B31" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>128354107</v>
       </c>
       <c r="B32" t="n">
-        <v>80135</v>
+        <v>80136</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128353959</v>
+        <v>128353844</v>
       </c>
       <c r="B33" t="n">
-        <v>80170</v>
+        <v>80171</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471204</v>
+        <v>471221</v>
       </c>
       <c r="R33" t="n">
-        <v>6871867</v>
+        <v>6871873</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4001,10 +4001,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128353844</v>
+        <v>128353959</v>
       </c>
       <c r="B34" t="n">
-        <v>80170</v>
+        <v>80171</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471221</v>
+        <v>471204</v>
       </c>
       <c r="R34" t="n">
-        <v>6871873</v>
+        <v>6871867</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>128353772</v>
       </c>
       <c r="B25" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128353867</v>
       </c>
       <c r="B26" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128353668</v>
       </c>
       <c r="B27" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>128352854</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128354191</v>
       </c>
       <c r="B29" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>128352646</v>
       </c>
       <c r="B30" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128353533</v>
       </c>
       <c r="B31" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>128354107</v>
       </c>
       <c r="B32" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128353844</v>
       </c>
       <c r="B33" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128353959</v>
       </c>
       <c r="B34" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>128353772</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128353867</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128353668</v>
       </c>
       <c r="B27" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>128352854</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128354191</v>
       </c>
       <c r="B29" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>128352646</v>
       </c>
       <c r="B30" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128353533</v>
       </c>
       <c r="B31" t="n">
-        <v>79162</v>
+        <v>79166</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>128354107</v>
       </c>
       <c r="B32" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128353844</v>
       </c>
       <c r="B33" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128353959</v>
       </c>
       <c r="B34" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>128353772</v>
       </c>
       <c r="B25" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128353867</v>
       </c>
       <c r="B26" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128353668</v>
       </c>
       <c r="B27" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>128352854</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128354191</v>
       </c>
       <c r="B29" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>128352646</v>
       </c>
       <c r="B30" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128353533</v>
       </c>
       <c r="B31" t="n">
-        <v>79166</v>
+        <v>79168</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>128354107</v>
       </c>
       <c r="B32" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128353844</v>
       </c>
       <c r="B33" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128353959</v>
       </c>
       <c r="B34" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -3505,7 +3505,7 @@
         <v>128354191</v>
       </c>
       <c r="B29" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>128353772</v>
       </c>
       <c r="B25" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128353867</v>
       </c>
       <c r="B26" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128353668</v>
       </c>
       <c r="B27" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>128352854</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128354191</v>
       </c>
       <c r="B29" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>128352646</v>
       </c>
       <c r="B30" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128353533</v>
       </c>
       <c r="B31" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>128354107</v>
       </c>
       <c r="B32" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128353844</v>
       </c>
       <c r="B33" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128353959</v>
       </c>
       <c r="B34" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>128353772</v>
       </c>
       <c r="B25" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128353867</v>
       </c>
       <c r="B26" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128353668</v>
       </c>
       <c r="B27" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>128352854</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128354191</v>
       </c>
       <c r="B29" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>128352646</v>
       </c>
       <c r="B30" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128353533</v>
       </c>
       <c r="B31" t="n">
-        <v>79195</v>
+        <v>79199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>128354107</v>
       </c>
       <c r="B32" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128353844</v>
       </c>
       <c r="B33" t="n">
-        <v>80257</v>
+        <v>80261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128353959</v>
       </c>
       <c r="B34" t="n">
-        <v>80257</v>
+        <v>80261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>128353772</v>
       </c>
       <c r="B25" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>128353867</v>
       </c>
       <c r="B26" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>128353668</v>
       </c>
       <c r="B27" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>128352854</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>128354191</v>
       </c>
       <c r="B29" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>128352646</v>
       </c>
       <c r="B30" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128353533</v>
       </c>
       <c r="B31" t="n">
-        <v>79199</v>
+        <v>79203</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>128354107</v>
       </c>
       <c r="B32" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128353844</v>
       </c>
       <c r="B33" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128353959</v>
       </c>
       <c r="B34" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4096,6 +4096,103 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129014635</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79061</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>185</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sålnberget, Sålnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>471363</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6871802</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4101,7 +4101,7 @@
         <v>129014635</v>
       </c>
       <c r="B35" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4101,7 +4101,7 @@
         <v>129014635</v>
       </c>
       <c r="B35" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4101,7 +4101,7 @@
         <v>129014635</v>
       </c>
       <c r="B35" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4101,7 +4101,7 @@
         <v>129014635</v>
       </c>
       <c r="B35" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4101,7 +4101,7 @@
         <v>129014635</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4193,6 +4193,107 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131737914</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gropen Nord, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>471279</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6871951</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Christer Lindberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>131737914</v>
       </c>
       <c r="B36" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>131737914</v>
       </c>
       <c r="B36" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>131737914</v>
       </c>
       <c r="B36" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>131737914</v>
       </c>
       <c r="B36" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>131737914</v>
       </c>
       <c r="B36" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 42675-2025 artfynd.xlsx
+++ b/artfynd/A 42675-2025 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>131737914</v>
       </c>
       <c r="B36" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
